--- a/testprocess/1-process/集群随机启动/集群随机启动测试.xlsx
+++ b/testprocess/1-process/集群随机启动/集群随机启动测试.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="7980" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="7980" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="project-info" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="105">
   <si>
     <t>名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -335,6 +335,99 @@
   <si>
     <t>C:data</t>
     <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>testcase1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>testcase2</t>
+  </si>
+  <si>
+    <t>testcase3</t>
+  </si>
+  <si>
+    <t>testcase4</t>
+  </si>
+  <si>
+    <t>testcase5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>testcase6</t>
+  </si>
+  <si>
+    <t>testcase7</t>
+  </si>
+  <si>
+    <t>testcase8</t>
+  </si>
+  <si>
+    <t>testcase10</t>
+  </si>
+  <si>
+    <t>testcase11</t>
+  </si>
+  <si>
+    <t>testcase12</t>
+  </si>
+  <si>
+    <t>testcase14</t>
+  </si>
+  <si>
+    <t>testcase15</t>
+  </si>
+  <si>
+    <t>testcase16</t>
+  </si>
+  <si>
+    <t>testcase18</t>
+  </si>
+  <si>
+    <t>testcase19</t>
+  </si>
+  <si>
+    <t>testcase20</t>
+  </si>
+  <si>
+    <t>testcase9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>testcase13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>testcase17</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>通过随机启动集群的节点的方式来启动集群，在某些情况下会导致集群是启动失败的。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.启动了一个或多个data组的节点，如果在5分钟内集群中还没有cata主节点，那么集群启动失败</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.启动了一个或多个data组的节点，存在cata主节点，如果在5分钟内该data组不能选出主节点，那么集群启动失败</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.启动了一个或多个cata组的节点，如果在5分钟内该cata组不能选出主节点，那么集群启动失败</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在满足以下条件的随机启动集群，集群都会启动失败：（coord节点怎么随机启动都能正常启动，而且不会对cata和data组的节点启动产生影响）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.自动化测试用例  已提交到SVN 目录 4-testcase</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.把启动集群的操作集成到om中，用户可以通过web操作更好的控制集群的启停。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1158,6 +1251,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1182,75 +1281,78 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1301,15 +1403,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1614,10 +1707,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="49"/>
+      <c r="B1" s="51"/>
     </row>
     <row r="2" spans="1:3" ht="14.25" thickBot="1"/>
     <row r="3" spans="1:3" ht="25.5">
@@ -1679,110 +1772,110 @@
       </c>
     </row>
     <row r="9" spans="1:3" ht="40.5" customHeight="1">
-      <c r="A9" s="50" t="s">
+      <c r="A9" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="46" t="s">
+      <c r="B9" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="45" t="s">
+      <c r="C9" s="47" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="51"/>
-      <c r="B10" s="47"/>
-      <c r="C10" s="45"/>
+      <c r="A10" s="53"/>
+      <c r="B10" s="49"/>
+      <c r="C10" s="47"/>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="51"/>
-      <c r="B11" s="47"/>
-      <c r="C11" s="45"/>
+      <c r="A11" s="53"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="47"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="51"/>
-      <c r="B12" s="47"/>
-      <c r="C12" s="45"/>
+      <c r="A12" s="53"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="47"/>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="51"/>
-      <c r="B13" s="47"/>
-      <c r="C13" s="45"/>
+      <c r="A13" s="53"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="47"/>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="51"/>
-      <c r="B14" s="47"/>
-      <c r="C14" s="45"/>
+      <c r="A14" s="53"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="47"/>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="51"/>
-      <c r="B15" s="47"/>
-      <c r="C15" s="45"/>
+      <c r="A15" s="53"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="47"/>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="51"/>
-      <c r="B16" s="47"/>
-      <c r="C16" s="45"/>
+      <c r="A16" s="53"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="47"/>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="51"/>
-      <c r="B17" s="47"/>
-      <c r="C17" s="45"/>
+      <c r="A17" s="53"/>
+      <c r="B17" s="49"/>
+      <c r="C17" s="47"/>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="51"/>
-      <c r="B18" s="47"/>
-      <c r="C18" s="45"/>
+      <c r="A18" s="53"/>
+      <c r="B18" s="49"/>
+      <c r="C18" s="47"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="51"/>
-      <c r="B19" s="47"/>
-      <c r="C19" s="45"/>
+      <c r="A19" s="53"/>
+      <c r="B19" s="49"/>
+      <c r="C19" s="47"/>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="51"/>
-      <c r="B20" s="47"/>
-      <c r="C20" s="45"/>
+      <c r="A20" s="53"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="47"/>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="51"/>
-      <c r="B21" s="47"/>
-      <c r="C21" s="45"/>
+      <c r="A21" s="53"/>
+      <c r="B21" s="49"/>
+      <c r="C21" s="47"/>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="51"/>
-      <c r="B22" s="47"/>
-      <c r="C22" s="45"/>
+      <c r="A22" s="53"/>
+      <c r="B22" s="49"/>
+      <c r="C22" s="47"/>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="51"/>
-      <c r="B23" s="47"/>
-      <c r="C23" s="45"/>
+      <c r="A23" s="53"/>
+      <c r="B23" s="49"/>
+      <c r="C23" s="47"/>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="51"/>
-      <c r="B24" s="47"/>
-      <c r="C24" s="45"/>
+      <c r="A24" s="53"/>
+      <c r="B24" s="49"/>
+      <c r="C24" s="47"/>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="51"/>
-      <c r="B25" s="47"/>
-      <c r="C25" s="45"/>
+      <c r="A25" s="53"/>
+      <c r="B25" s="49"/>
+      <c r="C25" s="47"/>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="51"/>
-      <c r="B26" s="47"/>
-      <c r="C26" s="45"/>
+      <c r="A26" s="53"/>
+      <c r="B26" s="49"/>
+      <c r="C26" s="47"/>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="51"/>
-      <c r="B27" s="47"/>
-      <c r="C27" s="45"/>
+      <c r="A27" s="53"/>
+      <c r="B27" s="49"/>
+      <c r="C27" s="47"/>
     </row>
     <row r="28" spans="1:3" ht="14.25" thickBot="1">
-      <c r="A28" s="52"/>
-      <c r="B28" s="48"/>
-      <c r="C28" s="45"/>
+      <c r="A28" s="54"/>
+      <c r="B28" s="50"/>
+      <c r="C28" s="47"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1808,232 +1901,234 @@
     <col min="5" max="5" width="10.375" style="25" customWidth="1"/>
     <col min="6" max="6" width="9" style="25"/>
     <col min="7" max="7" width="11.75" style="25" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="25"/>
+    <col min="8" max="8" width="9" style="25"/>
+    <col min="9" max="9" width="15.875" style="25" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="25"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="22.5" customHeight="1">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="79" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
     </row>
     <row r="3" spans="1:9" ht="14.25" thickBot="1">
-      <c r="A3" s="81" t="s">
+      <c r="A3" s="84" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="81"/>
-      <c r="C3" s="81"/>
-      <c r="D3" s="81"/>
-      <c r="E3" s="81"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="81"/>
+      <c r="B3" s="84"/>
+      <c r="C3" s="84"/>
+      <c r="D3" s="84"/>
+      <c r="E3" s="84"/>
+      <c r="F3" s="84"/>
+      <c r="G3" s="84"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="82" t="s">
+      <c r="A4" s="85" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="89" t="s">
+      <c r="B4" s="92" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="54" t="s">
+      <c r="C4" s="55" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="54"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54" t="s">
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="H4" s="54"/>
-      <c r="I4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="56"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="83"/>
-      <c r="B5" s="61"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="56"/>
-      <c r="E5" s="56"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="56"/>
-      <c r="H5" s="56"/>
-      <c r="I5" s="57"/>
+      <c r="A5" s="86"/>
+      <c r="B5" s="62"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="58"/>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="83"/>
-      <c r="B6" s="90" t="s">
+      <c r="A6" s="86"/>
+      <c r="B6" s="93" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="60" t="s">
+      <c r="C6" s="61" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="60"/>
-      <c r="E6" s="60"/>
-      <c r="F6" s="56"/>
-      <c r="G6" s="56"/>
-      <c r="H6" s="56"/>
-      <c r="I6" s="57"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="61"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="58"/>
     </row>
     <row r="7" spans="1:9" ht="14.25" thickBot="1">
-      <c r="A7" s="84"/>
-      <c r="B7" s="61"/>
-      <c r="C7" s="60"/>
-      <c r="D7" s="60"/>
-      <c r="E7" s="60"/>
-      <c r="F7" s="56"/>
-      <c r="G7" s="56"/>
-      <c r="H7" s="56"/>
-      <c r="I7" s="57"/>
+      <c r="A7" s="87"/>
+      <c r="B7" s="62"/>
+      <c r="C7" s="61"/>
+      <c r="D7" s="61"/>
+      <c r="E7" s="61"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="57"/>
+      <c r="H7" s="57"/>
+      <c r="I7" s="58"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="88" t="s">
+      <c r="A8" s="91" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="61" t="s">
+      <c r="B8" s="62" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="56"/>
-      <c r="D8" s="56"/>
-      <c r="E8" s="56"/>
-      <c r="F8" s="56"/>
-      <c r="G8" s="56"/>
-      <c r="H8" s="56"/>
-      <c r="I8" s="57"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="58"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="83"/>
-      <c r="B9" s="61"/>
-      <c r="C9" s="56"/>
-      <c r="D9" s="56"/>
-      <c r="E9" s="56"/>
-      <c r="F9" s="56"/>
-      <c r="G9" s="56"/>
-      <c r="H9" s="56"/>
-      <c r="I9" s="57"/>
+      <c r="A9" s="86"/>
+      <c r="B9" s="62"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="58"/>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="83"/>
-      <c r="B10" s="61" t="s">
+      <c r="A10" s="86"/>
+      <c r="B10" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="56"/>
-      <c r="D10" s="56"/>
-      <c r="E10" s="56"/>
-      <c r="F10" s="56"/>
-      <c r="G10" s="56"/>
-      <c r="H10" s="56"/>
-      <c r="I10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="57"/>
+      <c r="I10" s="58"/>
     </row>
     <row r="11" spans="1:9" ht="14.25" thickBot="1">
-      <c r="A11" s="84"/>
-      <c r="B11" s="62"/>
-      <c r="C11" s="58"/>
-      <c r="D11" s="58"/>
-      <c r="E11" s="58"/>
-      <c r="F11" s="58"/>
-      <c r="G11" s="58"/>
-      <c r="H11" s="58"/>
-      <c r="I11" s="59"/>
+      <c r="A11" s="87"/>
+      <c r="B11" s="63"/>
+      <c r="C11" s="59"/>
+      <c r="D11" s="59"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="59"/>
+      <c r="H11" s="59"/>
+      <c r="I11" s="60"/>
     </row>
     <row r="17" spans="1:9" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A17" s="80" t="s">
+      <c r="A17" s="83" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="80"/>
-      <c r="C17" s="80"/>
-      <c r="D17" s="80"/>
-      <c r="E17" s="80"/>
-      <c r="F17" s="80"/>
-      <c r="G17" s="80"/>
+      <c r="B17" s="83"/>
+      <c r="C17" s="83"/>
+      <c r="D17" s="83"/>
+      <c r="E17" s="83"/>
+      <c r="F17" s="83"/>
+      <c r="G17" s="83"/>
     </row>
     <row r="18" spans="1:9" ht="33.75" customHeight="1">
-      <c r="A18" s="77" t="s">
+      <c r="A18" s="80" t="s">
         <v>22</v>
       </c>
       <c r="B18" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="54" t="s">
+      <c r="C18" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="54"/>
-      <c r="E18" s="54"/>
+      <c r="D18" s="55"/>
+      <c r="E18" s="55"/>
       <c r="F18" s="38"/>
-      <c r="G18" s="54" t="s">
+      <c r="G18" s="55" t="s">
         <v>31</v>
       </c>
-      <c r="H18" s="54"/>
-      <c r="I18" s="55"/>
+      <c r="H18" s="55"/>
+      <c r="I18" s="56"/>
     </row>
     <row r="19" spans="1:9" ht="21.75" customHeight="1">
-      <c r="A19" s="78"/>
+      <c r="A19" s="81"/>
       <c r="B19" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="63"/>
-      <c r="D19" s="64"/>
-      <c r="E19" s="61"/>
+      <c r="C19" s="64"/>
+      <c r="D19" s="65"/>
+      <c r="E19" s="62"/>
       <c r="F19" s="39"/>
-      <c r="G19" s="70"/>
-      <c r="H19" s="71"/>
-      <c r="I19" s="72"/>
+      <c r="G19" s="71"/>
+      <c r="H19" s="72"/>
+      <c r="I19" s="73"/>
     </row>
     <row r="20" spans="1:9" ht="18" customHeight="1">
-      <c r="A20" s="78"/>
+      <c r="A20" s="81"/>
       <c r="B20" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="65" t="s">
+      <c r="C20" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="66"/>
-      <c r="E20" s="67"/>
+      <c r="D20" s="67"/>
+      <c r="E20" s="68"/>
       <c r="F20" s="40"/>
-      <c r="G20" s="73"/>
-      <c r="H20" s="74"/>
-      <c r="I20" s="75"/>
+      <c r="G20" s="74"/>
+      <c r="H20" s="75"/>
+      <c r="I20" s="76"/>
     </row>
     <row r="21" spans="1:9" ht="21.75" customHeight="1">
-      <c r="A21" s="78"/>
+      <c r="A21" s="81"/>
       <c r="B21" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="63"/>
-      <c r="D21" s="64"/>
-      <c r="E21" s="61"/>
+      <c r="C21" s="64"/>
+      <c r="D21" s="65"/>
+      <c r="E21" s="62"/>
       <c r="F21" s="39"/>
-      <c r="G21" s="70"/>
-      <c r="H21" s="71"/>
-      <c r="I21" s="72"/>
+      <c r="G21" s="71"/>
+      <c r="H21" s="72"/>
+      <c r="I21" s="73"/>
     </row>
     <row r="22" spans="1:9" ht="18.75" customHeight="1" thickBot="1">
-      <c r="A22" s="79"/>
+      <c r="A22" s="82"/>
       <c r="B22" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="68"/>
-      <c r="D22" s="69"/>
-      <c r="E22" s="62"/>
+      <c r="C22" s="69"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="63"/>
       <c r="F22" s="41"/>
-      <c r="G22" s="85"/>
-      <c r="H22" s="86"/>
-      <c r="I22" s="87"/>
+      <c r="G22" s="88"/>
+      <c r="H22" s="89"/>
+      <c r="I22" s="90"/>
     </row>
     <row r="27" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A27" s="93" t="s">
+      <c r="A27" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="B27" s="94"/>
-      <c r="C27" s="94"/>
-      <c r="D27" s="94"/>
-      <c r="E27" s="94"/>
-      <c r="F27" s="94"/>
-      <c r="G27" s="94"/>
+      <c r="B27" s="46"/>
+      <c r="C27" s="46"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="46"/>
+      <c r="F27" s="46"/>
+      <c r="G27" s="46"/>
     </row>
     <row r="28" spans="1:9" ht="27">
-      <c r="A28" s="60" t="s">
+      <c r="A28" s="61" t="s">
         <v>59</v>
       </c>
       <c r="B28" s="42"/>
@@ -2058,7 +2153,7 @@
       </c>
     </row>
     <row r="29" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A29" s="60"/>
+      <c r="A29" s="61"/>
       <c r="B29" s="42"/>
       <c r="C29" s="43" t="s">
         <v>64</v>
@@ -2076,10 +2171,12 @@
         <v>67</v>
       </c>
       <c r="H29" s="43"/>
-      <c r="I29" s="43"/>
+      <c r="I29" s="43" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="60"/>
+      <c r="A30" s="61"/>
       <c r="B30" s="42"/>
       <c r="C30" s="43" t="s">
         <v>64</v>
@@ -2097,10 +2194,12 @@
         <v>67</v>
       </c>
       <c r="H30" s="43"/>
-      <c r="I30" s="43"/>
+      <c r="I30" s="43" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="60"/>
+      <c r="A31" s="61"/>
       <c r="B31" s="42"/>
       <c r="C31" s="43" t="s">
         <v>64</v>
@@ -2118,10 +2217,12 @@
         <v>67</v>
       </c>
       <c r="H31" s="43"/>
-      <c r="I31" s="43"/>
+      <c r="I31" s="43" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="60"/>
+      <c r="A32" s="61"/>
       <c r="B32" s="42"/>
       <c r="C32" s="43" t="s">
         <v>64</v>
@@ -2139,26 +2240,28 @@
         <v>67</v>
       </c>
       <c r="H32" s="43"/>
-      <c r="I32" s="43"/>
+      <c r="I32" s="43" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="37" spans="1:9">
-      <c r="A37" s="93" t="s">
+      <c r="A37" s="45" t="s">
         <v>60</v>
       </c>
-      <c r="B37" s="93"/>
-      <c r="C37" s="93"/>
-      <c r="D37" s="93" t="s">
+      <c r="B37" s="45"/>
+      <c r="C37" s="45"/>
+      <c r="D37" s="45" t="s">
         <v>75</v>
       </c>
-      <c r="E37" s="93" t="s">
+      <c r="E37" s="45" t="s">
         <v>76</v>
       </c>
-      <c r="F37" s="93" t="s">
+      <c r="F37" s="45" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="27">
-      <c r="A38" s="95" t="s">
+      <c r="A38" s="77" t="s">
         <v>61</v>
       </c>
       <c r="B38" s="42"/>
@@ -2183,7 +2286,7 @@
       </c>
     </row>
     <row r="39" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A39" s="53"/>
+      <c r="A39" s="78"/>
       <c r="B39" s="42"/>
       <c r="C39" s="43" t="s">
         <v>71</v>
@@ -2203,10 +2306,12 @@
       <c r="H39" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="I39" s="43"/>
+      <c r="I39" s="43" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="40" spans="1:9">
-      <c r="A40" s="53"/>
+      <c r="A40" s="78"/>
       <c r="B40" s="42"/>
       <c r="C40" s="43" t="s">
         <v>71</v>
@@ -2226,10 +2331,12 @@
       <c r="H40" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="I40" s="43"/>
+      <c r="I40" s="43" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="41" spans="1:9">
-      <c r="A41" s="53"/>
+      <c r="A41" s="78"/>
       <c r="B41" s="42"/>
       <c r="C41" s="43" t="s">
         <v>71</v>
@@ -2249,10 +2356,12 @@
       <c r="H41" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="I41" s="43"/>
+      <c r="I41" s="43" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="42" spans="1:9">
-      <c r="A42" s="53"/>
+      <c r="A42" s="78"/>
       <c r="B42" s="42"/>
       <c r="C42" s="43" t="s">
         <v>71</v>
@@ -2272,10 +2381,12 @@
       <c r="H42" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="I42" s="43"/>
+      <c r="I42" s="43" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="43" spans="1:9">
-      <c r="A43" s="53"/>
+      <c r="A43" s="78"/>
       <c r="B43" s="42"/>
       <c r="C43" s="43"/>
       <c r="D43" s="43"/>
@@ -2286,7 +2397,7 @@
       <c r="I43" s="43"/>
     </row>
     <row r="44" spans="1:9">
-      <c r="A44" s="53"/>
+      <c r="A44" s="78"/>
       <c r="B44" s="42"/>
       <c r="C44" s="43" t="s">
         <v>71</v>
@@ -2306,10 +2417,12 @@
       <c r="H44" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="I44" s="43"/>
+      <c r="I44" s="43" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="45" spans="1:9">
-      <c r="A45" s="53"/>
+      <c r="A45" s="78"/>
       <c r="B45" s="42"/>
       <c r="C45" s="43" t="s">
         <v>71</v>
@@ -2329,10 +2442,12 @@
       <c r="H45" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="I45" s="43"/>
+      <c r="I45" s="43" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="46" spans="1:9">
-      <c r="A46" s="53"/>
+      <c r="A46" s="78"/>
       <c r="B46" s="42"/>
       <c r="C46" s="43" t="s">
         <v>71</v>
@@ -2352,10 +2467,12 @@
       <c r="H46" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="I46" s="43"/>
+      <c r="I46" s="43" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="47" spans="1:9">
-      <c r="A47" s="53"/>
+      <c r="A47" s="78"/>
       <c r="B47" s="42"/>
       <c r="C47" s="43" t="s">
         <v>71</v>
@@ -2375,10 +2492,12 @@
       <c r="H47" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="I47" s="43"/>
+      <c r="I47" s="43" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="48" spans="1:9">
-      <c r="A48" s="53"/>
+      <c r="A48" s="78"/>
       <c r="B48" s="42"/>
       <c r="C48" s="43"/>
       <c r="D48" s="43"/>
@@ -2389,7 +2508,7 @@
       <c r="I48" s="43"/>
     </row>
     <row r="49" spans="1:9">
-      <c r="A49" s="53"/>
+      <c r="A49" s="78"/>
       <c r="B49" s="42"/>
       <c r="C49" s="43" t="s">
         <v>71</v>
@@ -2409,10 +2528,12 @@
       <c r="H49" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="I49" s="43"/>
+      <c r="I49" s="43" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="50" spans="1:9">
-      <c r="A50" s="53"/>
+      <c r="A50" s="78"/>
       <c r="B50" s="42"/>
       <c r="C50" s="43" t="s">
         <v>71</v>
@@ -2432,10 +2553,12 @@
       <c r="H50" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="I50" s="43"/>
+      <c r="I50" s="43" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="51" spans="1:9">
-      <c r="A51" s="53"/>
+      <c r="A51" s="78"/>
       <c r="B51" s="42"/>
       <c r="C51" s="43" t="s">
         <v>71</v>
@@ -2455,10 +2578,12 @@
       <c r="H51" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="I51" s="43"/>
+      <c r="I51" s="43" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="52" spans="1:9">
-      <c r="A52" s="53"/>
+      <c r="A52" s="78"/>
       <c r="B52" s="42"/>
       <c r="C52" s="43" t="s">
         <v>71</v>
@@ -2478,10 +2603,12 @@
       <c r="H52" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="I52" s="43"/>
+      <c r="I52" s="43" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="53" spans="1:9">
-      <c r="A53" s="53"/>
+      <c r="A53" s="78"/>
       <c r="B53" s="42"/>
       <c r="C53" s="43"/>
       <c r="D53" s="43"/>
@@ -2492,7 +2619,7 @@
       <c r="I53" s="43"/>
     </row>
     <row r="54" spans="1:9">
-      <c r="A54" s="53"/>
+      <c r="A54" s="78"/>
       <c r="B54" s="42"/>
       <c r="C54" s="43" t="s">
         <v>71</v>
@@ -2512,10 +2639,12 @@
       <c r="H54" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="I54" s="43"/>
+      <c r="I54" s="43" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="55" spans="1:9">
-      <c r="A55" s="53"/>
+      <c r="A55" s="78"/>
       <c r="B55" s="42"/>
       <c r="C55" s="43" t="s">
         <v>71</v>
@@ -2535,10 +2664,12 @@
       <c r="H55" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="I55" s="43"/>
+      <c r="I55" s="43" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="56" spans="1:9">
-      <c r="A56" s="53"/>
+      <c r="A56" s="78"/>
       <c r="B56" s="42"/>
       <c r="C56" s="43" t="s">
         <v>71</v>
@@ -2558,10 +2689,12 @@
       <c r="H56" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="I56" s="43"/>
+      <c r="I56" s="43" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="57" spans="1:9">
-      <c r="A57" s="53"/>
+      <c r="A57" s="78"/>
       <c r="B57" s="42"/>
       <c r="C57" s="43" t="s">
         <v>71</v>
@@ -2581,10 +2714,16 @@
       <c r="H57" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="I57" s="43"/>
+      <c r="I57" s="43" t="s">
+        <v>94</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="G20:I20"/>
     <mergeCell ref="A38:A57"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A18:A22"/>
@@ -2599,14 +2738,6 @@
     <mergeCell ref="C8:E9"/>
     <mergeCell ref="C10:E11"/>
     <mergeCell ref="A8:A11"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="G20:I20"/>
     <mergeCell ref="G4:I5"/>
     <mergeCell ref="G6:I7"/>
     <mergeCell ref="G8:I9"/>
@@ -2619,6 +2750,10 @@
     <mergeCell ref="F8:F9"/>
     <mergeCell ref="F10:F11"/>
     <mergeCell ref="G18:I18"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C22:E22"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2649,8 +2784,8 @@
       <c r="A2" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="91"/>
-      <c r="C2" s="92"/>
+      <c r="B2" s="94"/>
+      <c r="C2" s="95"/>
       <c r="D2" s="36"/>
     </row>
     <row r="3" spans="1:7" s="14" customFormat="1" ht="19.5" thickBot="1">
@@ -2680,10 +2815,10 @@
       <c r="C4" t="s">
         <v>57</v>
       </c>
-      <c r="F4" s="76" t="s">
+      <c r="F4" s="79" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="76"/>
+      <c r="G4" s="79"/>
     </row>
     <row r="5" spans="1:7">
       <c r="B5" s="18" t="s">
@@ -2692,12 +2827,12 @@
       <c r="C5" t="s">
         <v>56</v>
       </c>
-      <c r="F5" s="76"/>
-      <c r="G5" s="76"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="F6" s="76"/>
-      <c r="G6" s="76"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79"/>
     </row>
     <row r="7" spans="1:7">
       <c r="B7" s="44"/>
@@ -3322,7 +3457,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
@@ -3339,6 +3474,11 @@
       <c r="F1" s="22"/>
       <c r="G1" s="22"/>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>98</v>
+      </c>
+    </row>
     <row r="7" spans="1:7">
       <c r="A7" s="23" t="s">
         <v>44</v>
@@ -3350,6 +3490,26 @@
       <c r="F7" s="22"/>
       <c r="G7" s="22"/>
     </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>100</v>
+      </c>
+    </row>
     <row r="15" spans="1:7">
       <c r="A15" s="23" t="s">
         <v>46</v>
@@ -3361,6 +3521,11 @@
       <c r="F15" s="22"/>
       <c r="G15" s="22"/>
     </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>103</v>
+      </c>
+    </row>
     <row r="22" spans="1:7">
       <c r="A22" s="23" t="s">
         <v>47</v>
@@ -3371,6 +3536,11 @@
       <c r="E22" s="22"/>
       <c r="F22" s="22"/>
       <c r="G22" s="22"/>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" t="s">
+        <v>104</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/testprocess/1-process/集群随机启动/集群随机启动测试.xlsx
+++ b/testprocess/1-process/集群随机启动/集群随机启动测试.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="7980" activeTab="5"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="7980" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="project-info" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="107">
   <si>
     <t>名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -402,31 +402,39 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>通过随机启动集群的节点的方式来启动集群，在某些情况下会导致集群是启动失败的。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2.启动了一个或多个data组的节点，如果在5分钟内集群中还没有cata主节点，那么集群启动失败</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.启动了一个或多个data组的节点，存在cata主节点，如果在5分钟内该data组不能选出主节点，那么集群启动失败</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.启动了一个或多个cata组的节点，如果在5分钟内该cata组不能选出主节点，那么集群启动失败</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在满足以下条件的随机启动集群，集群都会启动失败：（coord节点怎么随机启动都能正常启动，而且不会对cata和data组的节点启动产生影响）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1.自动化测试用例  已提交到SVN 目录 4-testcase</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>1.把启动集群的操作集成到om中，用户可以通过web操作更好的控制集群的启停。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>随机启动集群的过程中，满足以下条件之一，集群都会启动失败：（coord节点怎么随机启动都能正常启动，而且不会对cata和data组的节点启动产生影响）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.启动了一个或多个cata组的节点，如果在5分钟内该cata组不能选出主节点，那么cata组启动失败，集群启动失败</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.启动了一个或多个data组的节点，如果在5分钟内集群中还没有cata主节点，那么cata组和data组启动失败，集群启动失败</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.启动了一个或多个data组的节点，存在cata主节点，如果在5分钟内该data组不能选出主节点，那么data组长启动失败，集群启动失败</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>通过随机启动集群的节点的方式来启动集群，在某些情况下会导致集群启动失败。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>结果项</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>√</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -434,7 +442,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -519,6 +527,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -1133,7 +1149,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1281,30 +1297,99 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1329,80 +1414,17 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1907,214 +1929,214 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="22.5" customHeight="1">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
     </row>
     <row r="3" spans="1:9" ht="14.25" thickBot="1">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="72" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="84"/>
-      <c r="C3" s="84"/>
-      <c r="D3" s="84"/>
-      <c r="E3" s="84"/>
-      <c r="F3" s="84"/>
-      <c r="G3" s="84"/>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="85" t="s">
+      <c r="A4" s="73" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="92" t="s">
+      <c r="B4" s="55" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="55" t="s">
+      <c r="C4" s="70" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55" t="s">
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="70" t="s">
         <v>42</v>
       </c>
-      <c r="H4" s="55"/>
-      <c r="I4" s="56"/>
+      <c r="H4" s="70"/>
+      <c r="I4" s="83"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="86"/>
-      <c r="B5" s="62"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="58"/>
+      <c r="A5" s="74"/>
+      <c r="B5" s="56"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="84"/>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="86"/>
-      <c r="B6" s="93" t="s">
+      <c r="A6" s="74"/>
+      <c r="B6" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="61" t="s">
+      <c r="C6" s="80" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="61"/>
-      <c r="E6" s="61"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="57"/>
-      <c r="I6" s="58"/>
+      <c r="D6" s="80"/>
+      <c r="E6" s="80"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="84"/>
     </row>
     <row r="7" spans="1:9" ht="14.25" thickBot="1">
-      <c r="A7" s="87"/>
-      <c r="B7" s="62"/>
-      <c r="C7" s="61"/>
-      <c r="D7" s="61"/>
-      <c r="E7" s="61"/>
-      <c r="F7" s="57"/>
-      <c r="G7" s="57"/>
-      <c r="H7" s="57"/>
-      <c r="I7" s="58"/>
+      <c r="A7" s="75"/>
+      <c r="B7" s="56"/>
+      <c r="C7" s="80"/>
+      <c r="D7" s="80"/>
+      <c r="E7" s="80"/>
+      <c r="F7" s="79"/>
+      <c r="G7" s="79"/>
+      <c r="H7" s="79"/>
+      <c r="I7" s="84"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="91" t="s">
+      <c r="A8" s="82" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="62" t="s">
+      <c r="B8" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="58"/>
+      <c r="C8" s="79"/>
+      <c r="D8" s="79"/>
+      <c r="E8" s="79"/>
+      <c r="F8" s="79"/>
+      <c r="G8" s="79"/>
+      <c r="H8" s="79"/>
+      <c r="I8" s="84"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="86"/>
-      <c r="B9" s="62"/>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="58"/>
+      <c r="A9" s="74"/>
+      <c r="B9" s="56"/>
+      <c r="C9" s="79"/>
+      <c r="D9" s="79"/>
+      <c r="E9" s="79"/>
+      <c r="F9" s="79"/>
+      <c r="G9" s="79"/>
+      <c r="H9" s="79"/>
+      <c r="I9" s="84"/>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="86"/>
-      <c r="B10" s="62" t="s">
+      <c r="A10" s="74"/>
+      <c r="B10" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="57"/>
-      <c r="I10" s="58"/>
+      <c r="C10" s="79"/>
+      <c r="D10" s="79"/>
+      <c r="E10" s="79"/>
+      <c r="F10" s="79"/>
+      <c r="G10" s="79"/>
+      <c r="H10" s="79"/>
+      <c r="I10" s="84"/>
     </row>
     <row r="11" spans="1:9" ht="14.25" thickBot="1">
-      <c r="A11" s="87"/>
-      <c r="B11" s="63"/>
-      <c r="C11" s="59"/>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="59"/>
-      <c r="H11" s="59"/>
-      <c r="I11" s="60"/>
+      <c r="A11" s="75"/>
+      <c r="B11" s="86"/>
+      <c r="C11" s="81"/>
+      <c r="D11" s="81"/>
+      <c r="E11" s="81"/>
+      <c r="F11" s="81"/>
+      <c r="G11" s="81"/>
+      <c r="H11" s="81"/>
+      <c r="I11" s="85"/>
     </row>
     <row r="17" spans="1:9" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A17" s="83" t="s">
+      <c r="A17" s="71" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="83"/>
-      <c r="C17" s="83"/>
-      <c r="D17" s="83"/>
-      <c r="E17" s="83"/>
-      <c r="F17" s="83"/>
-      <c r="G17" s="83"/>
+      <c r="B17" s="71"/>
+      <c r="C17" s="71"/>
+      <c r="D17" s="71"/>
+      <c r="E17" s="71"/>
+      <c r="F17" s="71"/>
+      <c r="G17" s="71"/>
     </row>
     <row r="18" spans="1:9" ht="33.75" customHeight="1">
-      <c r="A18" s="80" t="s">
+      <c r="A18" s="67" t="s">
         <v>22</v>
       </c>
       <c r="B18" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="55" t="s">
+      <c r="C18" s="70" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="55"/>
-      <c r="E18" s="55"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="70"/>
       <c r="F18" s="38"/>
-      <c r="G18" s="55" t="s">
+      <c r="G18" s="70" t="s">
         <v>31</v>
       </c>
-      <c r="H18" s="55"/>
-      <c r="I18" s="56"/>
+      <c r="H18" s="70"/>
+      <c r="I18" s="83"/>
     </row>
     <row r="19" spans="1:9" ht="21.75" customHeight="1">
-      <c r="A19" s="81"/>
+      <c r="A19" s="68"/>
       <c r="B19" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="64"/>
-      <c r="D19" s="65"/>
-      <c r="E19" s="62"/>
+      <c r="C19" s="87"/>
+      <c r="D19" s="88"/>
+      <c r="E19" s="56"/>
       <c r="F19" s="39"/>
-      <c r="G19" s="71"/>
-      <c r="H19" s="72"/>
-      <c r="I19" s="73"/>
+      <c r="G19" s="58"/>
+      <c r="H19" s="59"/>
+      <c r="I19" s="60"/>
     </row>
     <row r="20" spans="1:9" ht="18" customHeight="1">
-      <c r="A20" s="81"/>
+      <c r="A20" s="68"/>
       <c r="B20" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="66" t="s">
+      <c r="C20" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="67"/>
-      <c r="E20" s="68"/>
+      <c r="D20" s="90"/>
+      <c r="E20" s="91"/>
       <c r="F20" s="40"/>
-      <c r="G20" s="74"/>
-      <c r="H20" s="75"/>
-      <c r="I20" s="76"/>
+      <c r="G20" s="61"/>
+      <c r="H20" s="62"/>
+      <c r="I20" s="63"/>
     </row>
     <row r="21" spans="1:9" ht="21.75" customHeight="1">
-      <c r="A21" s="81"/>
+      <c r="A21" s="68"/>
       <c r="B21" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="64"/>
-      <c r="D21" s="65"/>
-      <c r="E21" s="62"/>
+      <c r="C21" s="87"/>
+      <c r="D21" s="88"/>
+      <c r="E21" s="56"/>
       <c r="F21" s="39"/>
-      <c r="G21" s="71"/>
-      <c r="H21" s="72"/>
-      <c r="I21" s="73"/>
+      <c r="G21" s="58"/>
+      <c r="H21" s="59"/>
+      <c r="I21" s="60"/>
     </row>
     <row r="22" spans="1:9" ht="18.75" customHeight="1" thickBot="1">
-      <c r="A22" s="82"/>
+      <c r="A22" s="69"/>
       <c r="B22" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="69"/>
-      <c r="D22" s="70"/>
-      <c r="E22" s="63"/>
+      <c r="C22" s="92"/>
+      <c r="D22" s="93"/>
+      <c r="E22" s="86"/>
       <c r="F22" s="41"/>
-      <c r="G22" s="88"/>
-      <c r="H22" s="89"/>
-      <c r="I22" s="90"/>
+      <c r="G22" s="76"/>
+      <c r="H22" s="77"/>
+      <c r="I22" s="78"/>
     </row>
     <row r="27" spans="1:9" ht="14.25" customHeight="1">
       <c r="A27" s="45" t="s">
@@ -2128,7 +2150,7 @@
       <c r="G27" s="46"/>
     </row>
     <row r="28" spans="1:9" ht="27">
-      <c r="A28" s="61" t="s">
+      <c r="A28" s="80" t="s">
         <v>59</v>
       </c>
       <c r="B28" s="42"/>
@@ -2153,7 +2175,7 @@
       </c>
     </row>
     <row r="29" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A29" s="61"/>
+      <c r="A29" s="80"/>
       <c r="B29" s="42"/>
       <c r="C29" s="43" t="s">
         <v>64</v>
@@ -2176,7 +2198,7 @@
       </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="61"/>
+      <c r="A30" s="80"/>
       <c r="B30" s="42"/>
       <c r="C30" s="43" t="s">
         <v>64</v>
@@ -2199,7 +2221,7 @@
       </c>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="61"/>
+      <c r="A31" s="80"/>
       <c r="B31" s="42"/>
       <c r="C31" s="43" t="s">
         <v>64</v>
@@ -2222,7 +2244,7 @@
       </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="61"/>
+      <c r="A32" s="80"/>
       <c r="B32" s="42"/>
       <c r="C32" s="43" t="s">
         <v>64</v>
@@ -2261,7 +2283,7 @@
       </c>
     </row>
     <row r="38" spans="1:9" ht="27">
-      <c r="A38" s="77" t="s">
+      <c r="A38" s="64" t="s">
         <v>61</v>
       </c>
       <c r="B38" s="42"/>
@@ -2286,7 +2308,7 @@
       </c>
     </row>
     <row r="39" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A39" s="78"/>
+      <c r="A39" s="65"/>
       <c r="B39" s="42"/>
       <c r="C39" s="43" t="s">
         <v>71</v>
@@ -2311,7 +2333,7 @@
       </c>
     </row>
     <row r="40" spans="1:9">
-      <c r="A40" s="78"/>
+      <c r="A40" s="65"/>
       <c r="B40" s="42"/>
       <c r="C40" s="43" t="s">
         <v>71</v>
@@ -2336,7 +2358,7 @@
       </c>
     </row>
     <row r="41" spans="1:9">
-      <c r="A41" s="78"/>
+      <c r="A41" s="65"/>
       <c r="B41" s="42"/>
       <c r="C41" s="43" t="s">
         <v>71</v>
@@ -2361,7 +2383,7 @@
       </c>
     </row>
     <row r="42" spans="1:9">
-      <c r="A42" s="78"/>
+      <c r="A42" s="65"/>
       <c r="B42" s="42"/>
       <c r="C42" s="43" t="s">
         <v>71</v>
@@ -2386,7 +2408,7 @@
       </c>
     </row>
     <row r="43" spans="1:9">
-      <c r="A43" s="78"/>
+      <c r="A43" s="65"/>
       <c r="B43" s="42"/>
       <c r="C43" s="43"/>
       <c r="D43" s="43"/>
@@ -2397,7 +2419,7 @@
       <c r="I43" s="43"/>
     </row>
     <row r="44" spans="1:9">
-      <c r="A44" s="78"/>
+      <c r="A44" s="65"/>
       <c r="B44" s="42"/>
       <c r="C44" s="43" t="s">
         <v>71</v>
@@ -2422,7 +2444,7 @@
       </c>
     </row>
     <row r="45" spans="1:9">
-      <c r="A45" s="78"/>
+      <c r="A45" s="65"/>
       <c r="B45" s="42"/>
       <c r="C45" s="43" t="s">
         <v>71</v>
@@ -2447,7 +2469,7 @@
       </c>
     </row>
     <row r="46" spans="1:9">
-      <c r="A46" s="78"/>
+      <c r="A46" s="65"/>
       <c r="B46" s="42"/>
       <c r="C46" s="43" t="s">
         <v>71</v>
@@ -2472,7 +2494,7 @@
       </c>
     </row>
     <row r="47" spans="1:9">
-      <c r="A47" s="78"/>
+      <c r="A47" s="65"/>
       <c r="B47" s="42"/>
       <c r="C47" s="43" t="s">
         <v>71</v>
@@ -2497,7 +2519,7 @@
       </c>
     </row>
     <row r="48" spans="1:9">
-      <c r="A48" s="78"/>
+      <c r="A48" s="65"/>
       <c r="B48" s="42"/>
       <c r="C48" s="43"/>
       <c r="D48" s="43"/>
@@ -2508,7 +2530,7 @@
       <c r="I48" s="43"/>
     </row>
     <row r="49" spans="1:9">
-      <c r="A49" s="78"/>
+      <c r="A49" s="65"/>
       <c r="B49" s="42"/>
       <c r="C49" s="43" t="s">
         <v>71</v>
@@ -2533,7 +2555,7 @@
       </c>
     </row>
     <row r="50" spans="1:9">
-      <c r="A50" s="78"/>
+      <c r="A50" s="65"/>
       <c r="B50" s="42"/>
       <c r="C50" s="43" t="s">
         <v>71</v>
@@ -2558,7 +2580,7 @@
       </c>
     </row>
     <row r="51" spans="1:9">
-      <c r="A51" s="78"/>
+      <c r="A51" s="65"/>
       <c r="B51" s="42"/>
       <c r="C51" s="43" t="s">
         <v>71</v>
@@ -2583,7 +2605,7 @@
       </c>
     </row>
     <row r="52" spans="1:9">
-      <c r="A52" s="78"/>
+      <c r="A52" s="65"/>
       <c r="B52" s="42"/>
       <c r="C52" s="43" t="s">
         <v>71</v>
@@ -2608,7 +2630,7 @@
       </c>
     </row>
     <row r="53" spans="1:9">
-      <c r="A53" s="78"/>
+      <c r="A53" s="65"/>
       <c r="B53" s="42"/>
       <c r="C53" s="43"/>
       <c r="D53" s="43"/>
@@ -2619,7 +2641,7 @@
       <c r="I53" s="43"/>
     </row>
     <row r="54" spans="1:9">
-      <c r="A54" s="78"/>
+      <c r="A54" s="65"/>
       <c r="B54" s="42"/>
       <c r="C54" s="43" t="s">
         <v>71</v>
@@ -2644,7 +2666,7 @@
       </c>
     </row>
     <row r="55" spans="1:9">
-      <c r="A55" s="78"/>
+      <c r="A55" s="65"/>
       <c r="B55" s="42"/>
       <c r="C55" s="43" t="s">
         <v>71</v>
@@ -2669,7 +2691,7 @@
       </c>
     </row>
     <row r="56" spans="1:9">
-      <c r="A56" s="78"/>
+      <c r="A56" s="65"/>
       <c r="B56" s="42"/>
       <c r="C56" s="43" t="s">
         <v>71</v>
@@ -2694,7 +2716,7 @@
       </c>
     </row>
     <row r="57" spans="1:9">
-      <c r="A57" s="78"/>
+      <c r="A57" s="65"/>
       <c r="B57" s="42"/>
       <c r="C57" s="43" t="s">
         <v>71</v>
@@ -2720,11 +2742,8 @@
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="A38:A57"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C22:E22"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A18:A22"/>
     <mergeCell ref="C18:E18"/>
@@ -2741,6 +2760,11 @@
     <mergeCell ref="G4:I5"/>
     <mergeCell ref="G6:I7"/>
     <mergeCell ref="G8:I9"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="A38:A57"/>
     <mergeCell ref="G10:I11"/>
     <mergeCell ref="A28:A32"/>
     <mergeCell ref="B8:B9"/>
@@ -2752,8 +2776,6 @@
     <mergeCell ref="G18:I18"/>
     <mergeCell ref="C19:E19"/>
     <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2815,10 +2837,10 @@
       <c r="C4" t="s">
         <v>57</v>
       </c>
-      <c r="F4" s="79" t="s">
+      <c r="F4" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="79"/>
+      <c r="G4" s="66"/>
     </row>
     <row r="5" spans="1:7">
       <c r="B5" s="18" t="s">
@@ -2827,12 +2849,12 @@
       <c r="C5" t="s">
         <v>56</v>
       </c>
-      <c r="F5" s="79"/>
-      <c r="G5" s="79"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="F6" s="79"/>
-      <c r="G6" s="79"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
     </row>
     <row r="7" spans="1:7">
       <c r="B7" s="44"/>
@@ -3447,11 +3469,696 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
-  <sheetData/>
+  <cols>
+    <col min="9" max="9" width="12.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="25" customFormat="1" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A1" s="45" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="96" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="25" customFormat="1" ht="27.75" thickBot="1">
+      <c r="A2" s="80" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2" s="42" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" s="42" t="s">
+        <v>62</v>
+      </c>
+      <c r="F2" s="42" t="s">
+        <v>63</v>
+      </c>
+      <c r="G2" s="42" t="s">
+        <v>62</v>
+      </c>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42" t="s">
+        <v>50</v>
+      </c>
+      <c r="J2" s="97"/>
+    </row>
+    <row r="3" spans="1:10" s="25" customFormat="1" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A3" s="80"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="43" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="E3" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="F3" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="G3" s="43" t="s">
+        <v>67</v>
+      </c>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43" t="s">
+        <v>78</v>
+      </c>
+      <c r="J3" s="97" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" s="25" customFormat="1" ht="14.25" thickBot="1">
+      <c r="A4" s="80"/>
+      <c r="B4" s="42"/>
+      <c r="C4" s="43" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="E4" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="F4" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="G4" s="43" t="s">
+        <v>67</v>
+      </c>
+      <c r="H4" s="43"/>
+      <c r="I4" s="43" t="s">
+        <v>79</v>
+      </c>
+      <c r="J4" s="97" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" s="25" customFormat="1" ht="14.25" thickBot="1">
+      <c r="A5" s="80"/>
+      <c r="B5" s="42"/>
+      <c r="C5" s="43" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="F5" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="G5" s="43" t="s">
+        <v>67</v>
+      </c>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="J5" s="97" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="25" customFormat="1">
+      <c r="A6" s="80"/>
+      <c r="B6" s="42"/>
+      <c r="C6" s="43" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="E6" s="43" t="s">
+        <v>66</v>
+      </c>
+      <c r="F6" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="G6" s="43" t="s">
+        <v>67</v>
+      </c>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43" t="s">
+        <v>81</v>
+      </c>
+      <c r="J6" s="97" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" s="25" customFormat="1"/>
+    <row r="8" spans="1:10" s="25" customFormat="1"/>
+    <row r="9" spans="1:10" s="25" customFormat="1"/>
+    <row r="10" spans="1:10" s="25" customFormat="1"/>
+    <row r="11" spans="1:10" s="25" customFormat="1" ht="14.25" thickBot="1">
+      <c r="A11" s="45" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="45"/>
+      <c r="C11" s="45"/>
+      <c r="D11" s="45" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="45" t="s">
+        <v>76</v>
+      </c>
+      <c r="F11" s="45" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" s="25" customFormat="1" ht="27.75" thickBot="1">
+      <c r="A12" s="64" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="42" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12" s="42" t="s">
+        <v>69</v>
+      </c>
+      <c r="G12" s="42" t="s">
+        <v>70</v>
+      </c>
+      <c r="H12" s="42" t="s">
+        <v>69</v>
+      </c>
+      <c r="I12" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="J12" s="97"/>
+    </row>
+    <row r="13" spans="1:10" s="25" customFormat="1" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A13" s="65"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="F13" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="G13" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="H13" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="I13" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="J13" s="97" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" s="25" customFormat="1" ht="16.5" customHeight="1" thickBot="1">
+      <c r="A14" s="65"/>
+      <c r="B14" s="42"/>
+      <c r="C14" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="D14" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="E14" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="F14" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="G14" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="H14" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="I14" s="43" t="s">
+        <v>83</v>
+      </c>
+      <c r="J14" s="97" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" s="25" customFormat="1" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A15" s="65"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="E15" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="F15" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="G15" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="H15" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="I15" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="J15" s="97" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" s="25" customFormat="1" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A16" s="65"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="D16" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="E16" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="F16" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="G16" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="H16" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="I16" s="43" t="s">
+        <v>85</v>
+      </c>
+      <c r="J16" s="97" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" s="25" customFormat="1" ht="14.25" thickBot="1">
+      <c r="A17" s="65"/>
+      <c r="B17" s="42"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="43"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="97"/>
+    </row>
+    <row r="18" spans="1:10" s="25" customFormat="1" ht="12.75" customHeight="1" thickBot="1">
+      <c r="A18" s="65"/>
+      <c r="B18" s="42"/>
+      <c r="C18" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="E18" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="F18" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="G18" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="H18" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="I18" s="43" t="s">
+        <v>95</v>
+      </c>
+      <c r="J18" s="97" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" s="25" customFormat="1" ht="17.25" customHeight="1" thickBot="1">
+      <c r="A19" s="65"/>
+      <c r="B19" s="42"/>
+      <c r="C19" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="D19" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="E19" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="F19" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="G19" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="H19" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="I19" s="43" t="s">
+        <v>86</v>
+      </c>
+      <c r="J19" s="97" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" s="25" customFormat="1" ht="12.75" customHeight="1" thickBot="1">
+      <c r="A20" s="65"/>
+      <c r="B20" s="42"/>
+      <c r="C20" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="D20" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="E20" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="F20" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="G20" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="H20" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="I20" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="J20" s="97" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" s="25" customFormat="1" ht="17.25" customHeight="1" thickBot="1">
+      <c r="A21" s="65"/>
+      <c r="B21" s="42"/>
+      <c r="C21" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="D21" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="E21" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="F21" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="G21" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="H21" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="I21" s="43" t="s">
+        <v>88</v>
+      </c>
+      <c r="J21" s="97" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" s="25" customFormat="1" ht="14.25" thickBot="1">
+      <c r="A22" s="65"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="43"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="97"/>
+    </row>
+    <row r="23" spans="1:10" s="25" customFormat="1" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A23" s="65"/>
+      <c r="B23" s="42"/>
+      <c r="C23" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="D23" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="E23" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="F23" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="G23" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="H23" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="I23" s="43" t="s">
+        <v>96</v>
+      </c>
+      <c r="J23" s="97" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" s="25" customFormat="1" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A24" s="65"/>
+      <c r="B24" s="42"/>
+      <c r="C24" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="D24" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="E24" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="F24" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="G24" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="H24" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="I24" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="J24" s="97" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" s="25" customFormat="1" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A25" s="65"/>
+      <c r="B25" s="42"/>
+      <c r="C25" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="D25" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="E25" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="F25" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="G25" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="H25" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="I25" s="43" t="s">
+        <v>90</v>
+      </c>
+      <c r="J25" s="97" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" s="25" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A26" s="65"/>
+      <c r="B26" s="42"/>
+      <c r="C26" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="D26" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="E26" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="F26" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="G26" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="H26" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="I26" s="43" t="s">
+        <v>91</v>
+      </c>
+      <c r="J26" s="97" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" s="25" customFormat="1" ht="14.25" thickBot="1">
+      <c r="A27" s="65"/>
+      <c r="B27" s="42"/>
+      <c r="C27" s="43"/>
+      <c r="D27" s="43"/>
+      <c r="E27" s="43"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="43"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="43"/>
+      <c r="J27" s="97"/>
+    </row>
+    <row r="28" spans="1:10" s="25" customFormat="1" ht="13.5" customHeight="1" thickBot="1">
+      <c r="A28" s="65"/>
+      <c r="B28" s="42"/>
+      <c r="C28" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="D28" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="E28" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="F28" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="G28" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="H28" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="I28" s="43" t="s">
+        <v>97</v>
+      </c>
+      <c r="J28" s="97" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" s="25" customFormat="1" ht="16.5" customHeight="1" thickBot="1">
+      <c r="A29" s="65"/>
+      <c r="B29" s="42"/>
+      <c r="C29" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="D29" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="E29" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="F29" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="G29" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="H29" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="I29" s="43" t="s">
+        <v>92</v>
+      </c>
+      <c r="J29" s="97" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" s="25" customFormat="1" ht="17.25" customHeight="1" thickBot="1">
+      <c r="A30" s="65"/>
+      <c r="B30" s="42"/>
+      <c r="C30" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="D30" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="E30" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="F30" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="G30" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="H30" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="I30" s="43" t="s">
+        <v>93</v>
+      </c>
+      <c r="J30" s="97" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" s="25" customFormat="1" ht="18" customHeight="1">
+      <c r="A31" s="65"/>
+      <c r="B31" s="42"/>
+      <c r="C31" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="D31" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="E31" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="F31" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="G31" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="H31" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="I31" s="43" t="s">
+        <v>94</v>
+      </c>
+      <c r="J31" s="97" t="s">
+        <v>106</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A12:A31"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3476,7 +4183,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>98</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -3492,22 +4214,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -3523,7 +4230,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -3539,7 +4246,7 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
